--- a/artfynd/A 56422-2023 artfynd.xlsx
+++ b/artfynd/A 56422-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125449091</v>
+        <v>125450689</v>
       </c>
       <c r="B2" t="n">
-        <v>78969</v>
+        <v>80029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438378</v>
+        <v>438330</v>
       </c>
       <c r="R2" t="n">
-        <v>7169278</v>
+        <v>7169127</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -768,22 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grannaturskog i kanten av en djup klyfta</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125450692</v>
+        <v>125450552</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438330</v>
+        <v>438315</v>
       </c>
       <c r="R3" t="n">
-        <v>7169127</v>
+        <v>7169148</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -894,7 +879,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
+          <t>Äldre granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125450109</v>
+        <v>125449091</v>
       </c>
       <c r="B4" t="n">
-        <v>78151</v>
+        <v>79106</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438336</v>
+        <v>438378</v>
       </c>
       <c r="R4" t="n">
-        <v>7169168</v>
+        <v>7169278</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Medelåldrig granskog med inslag av äldre och grövre granar</t>
+          <t>Grannaturskog i kanten av en djup klyfta</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125450684</v>
+        <v>125450692</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,25 +1050,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1353</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125450552</v>
+        <v>125450684</v>
       </c>
       <c r="B6" t="n">
-        <v>78891</v>
+        <v>79485</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>1353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438315</v>
+        <v>438330</v>
       </c>
       <c r="R6" t="n">
-        <v>7169148</v>
+        <v>7169127</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1242,22 +1242,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125450689</v>
+        <v>125450109</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>78288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438330</v>
+        <v>438336</v>
       </c>
       <c r="R7" t="n">
-        <v>7169127</v>
+        <v>7169168</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1368,7 +1353,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
+          <t>Medelåldrig granskog med inslag av äldre och grövre granar</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 56422-2023 artfynd.xlsx
+++ b/artfynd/A 56422-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125450689</v>
+        <v>125450692</v>
       </c>
       <c r="B2" t="n">
-        <v>80029</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125449091</v>
+        <v>125450109</v>
       </c>
       <c r="B4" t="n">
-        <v>79106</v>
+        <v>78288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438378</v>
+        <v>438336</v>
       </c>
       <c r="R4" t="n">
-        <v>7169278</v>
+        <v>7169168</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grannaturskog i kanten av en djup klyfta</t>
+          <t>Medelåldrig granskog med inslag av äldre och grövre granar</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125450692</v>
+        <v>125449091</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>79106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,25 +1050,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438330</v>
+        <v>438378</v>
       </c>
       <c r="R5" t="n">
-        <v>7169127</v>
+        <v>7169278</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1131,7 +1131,22 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
+          <t>Grannaturskog i kanten av en djup klyfta</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125450684</v>
+        <v>125450689</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>80029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1176,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1353</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1260,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125450109</v>
+        <v>125450684</v>
       </c>
       <c r="B7" t="n">
-        <v>78288</v>
+        <v>79485</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1287,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>1353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1303,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438336</v>
+        <v>438330</v>
       </c>
       <c r="R7" t="n">
-        <v>7169168</v>
+        <v>7169127</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1353,22 +1368,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Medelåldrig granskog med inslag av äldre och grövre granar</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 56422-2023 artfynd.xlsx
+++ b/artfynd/A 56422-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125450552</v>
       </c>
       <c r="B2" t="n">
-        <v>79048</v>
+        <v>79049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125450689</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125450109</v>
       </c>
       <c r="B4" t="n">
-        <v>78330</v>
+        <v>78331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>125450684</v>
       </c>
       <c r="B5" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>125449091</v>
       </c>
       <c r="B6" t="n">
-        <v>79126</v>
+        <v>79127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>125450692</v>
       </c>
       <c r="B7" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56422-2023 artfynd.xlsx
+++ b/artfynd/A 56422-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125450552</v>
       </c>
       <c r="B2" t="n">
-        <v>79049</v>
+        <v>79053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125450689</v>
       </c>
       <c r="B3" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125450109</v>
       </c>
       <c r="B4" t="n">
-        <v>78331</v>
+        <v>78335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>125450684</v>
       </c>
       <c r="B5" t="n">
-        <v>79506</v>
+        <v>79510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>125449091</v>
       </c>
       <c r="B6" t="n">
-        <v>79127</v>
+        <v>79131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>125450692</v>
       </c>
       <c r="B7" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56422-2023 artfynd.xlsx
+++ b/artfynd/A 56422-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125450552</v>
       </c>
       <c r="B2" t="n">
-        <v>79053</v>
+        <v>79054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125450689</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125450109</v>
       </c>
       <c r="B4" t="n">
-        <v>78335</v>
+        <v>78336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>125450684</v>
       </c>
       <c r="B5" t="n">
-        <v>79510</v>
+        <v>79511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>125449091</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>79132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>125450692</v>
       </c>
       <c r="B7" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56422-2023 artfynd.xlsx
+++ b/artfynd/A 56422-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125450552</v>
       </c>
       <c r="B2" t="n">
-        <v>79054</v>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125450689</v>
+        <v>125450109</v>
       </c>
       <c r="B3" t="n">
-        <v>80077</v>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438330</v>
+        <v>438336</v>
       </c>
       <c r="R3" t="n">
-        <v>7169127</v>
+        <v>7169168</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,7 +884,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
+          <t>Medelåldrig granskog med inslag av äldre och grövre granar</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125450109</v>
+        <v>125449091</v>
       </c>
       <c r="B4" t="n">
-        <v>78336</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438336</v>
+        <v>438378</v>
       </c>
       <c r="R4" t="n">
-        <v>7169168</v>
+        <v>7169278</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -990,7 +1005,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Medelåldrig granskog med inslag av äldre och grövre granar</t>
+          <t>Grannaturskog i kanten av en djup klyfta</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1026,7 +1041,7 @@
         <v>125450684</v>
       </c>
       <c r="B5" t="n">
-        <v>79511</v>
+        <v>79866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,32 +1144,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125449091</v>
+        <v>125450689</v>
       </c>
       <c r="B6" t="n">
-        <v>79132</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438378</v>
+        <v>438330</v>
       </c>
       <c r="R6" t="n">
-        <v>7169278</v>
+        <v>7169127</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1217,22 +1232,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grannaturskog i kanten av en djup klyfta</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Kalkrik lodyta i djup klyfta, beskuggad av gran och gråal</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1253,7 +1253,7 @@
         <v>125450692</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56422-2023 artfynd.xlsx
+++ b/artfynd/A 56422-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125450552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125450109</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125449091</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125450684</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125450689</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,8 +1383,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125450692</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>